--- a/stories/arbres/ATOM-FAM.VER.001-10.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-10.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Éric joue dans le salon. Un vase de fleurs penche. Il touche le vase. L'eau se répand. Éric a les mains mouillées. Son ventre est serré. Papa est dans la cuisine. Maman est près de la fenêtre. Éric va vers eux. Il va raconter. Il dit : j'ai touché le vase. L'eau est par terre. Papa écoute. Maman écoute. Papa dit : merci d'avoir raconté. On dit à papa ou maman ce qui s'est passé. Éric aide à essuyer. Maman dit : raconter, c'est le geste. Même quand c'est une bêtise. Plus tard, à la cuisine, de la farine tombe. Même leçon, autre lieu. Éric va raconter. Il dit à papa et maman : la farine est par terre. Papa sourit. Maman tend un torchon. Éric se sent plus léger.</t>
+          <t>Éric joue dans le salon. Un vase de fleurs penche. Il touche le vase. L'eau se répand. Éric a les mains mouillées. Son ventre est serré. Papa est dans la cuisine. Maman est près de la fenêtre. Éric va vers eux. Il va raconter. J'ai touché le vase. L'eau est par terre. Papa écoute. Maman écoute. Merci d'avoir raconté. On dit à papa ou maman ce qui s'est passé. Éric aide à essuyer. Raconter, c'est le geste. Même quand c'est une bêtise. Plus tard, à la cuisine, de la farine tombe. Même leçon, autre lieu. Éric va raconter. Il dit à papa et maman : la farine est par terre. Papa sourit. Maman tend un torchon. Éric se sent plus léger.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Éric joue dans le salon. Un vase de fleurs penche. Il touche le vase. L'eau se répand. Éric a les mains mouillées. Son ventre est serré. Papa est dans la cuisine. Maman est près de la fenêtre. Éric va vers eux. Il va raconter.
+narrateur|J'ai touché le vase. L'eau est par terre. Papa écoute. Maman écoute.
+papa|Merci d'avoir raconté. On dit à papa ou maman ce qui s'est passé.
+narrateur|Éric aide à essuyer.
+maman|Raconter, c'est le geste. Même quand c'est une bêtise. Plus tard, à la cuisine, de la farine tombe. Même leçon, autre lieu.
+narrateur|Éric va raconter. Il dit à papa et maman : la farine est par terre. Papa sourit. Maman tend un torchon. Éric se sent plus léger.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Éric a touché le vase. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Éric a su raconter. Il a parlé à papa et maman. Au salon, puis à la cuisine.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Éric pose le torchon. Maman lui tient la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-10.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-10.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Éric va raconter. Il dit à papa et maman : la farine est par terre. Papa sourit. Maman tend un torchon. Éric se sent plus léger.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Éric a touché le vase. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Éric a su raconter. Il a parlé à papa et maman. Au salon, puis à la cuisine.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1844,7 @@
           <t>narrateur|Éric pose le torchon. Maman lui tient la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.VER.001-10.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-10.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Éric raconte le vase</t>
+          <t>Raphaël raconte le vase</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le rideau se soulève. Raphaël raconte l'eau du vase, puis la farine. Papa et maman écoutent aux deux endroits.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Éric joue dans le salon. Un vase de fleurs penche. Il touche le vase. L'eau se répand. Éric a les mains mouillées. Son ventre est serré. Papa est dans la cuisine. Maman est près de la fenêtre. Éric va vers eux. Il va raconter. J'ai touché le vase. L'eau est par terre. Papa écoute. Maman écoute. Merci d'avoir raconté. On dit à papa ou maman ce qui s'est passé. Éric aide à essuyer. Raconter, c'est le geste. Même quand c'est une bêtise. Plus tard, à la cuisine, de la farine tombe. Même leçon, autre lieu. Éric va raconter. Il dit à papa et maman : la farine est par terre. Papa sourit. Maman tend un torchon. Éric se sent plus léger.</t>
+          <t>Le rideau se soulève un tout petit peu. Un vent doux entre. Une abeille tape la vitre, puis s'en va. Des fleurs jaunes sont dans un vase. L'eau du vase brille. Une tige penche vers la lumière. Papa est dans la cuisine. Ça sent le pain chaud, là-bas. Maman est près de la fenêtre. Raphaël, tu as vu l'abeille ? Oui, maman. Elle est partie. Elle a tapé tout doux. Le pain est presque prêt. En ce moment, Raphaël s'approche du vase. Les fleurs sentent l'herbe coupée. Il touche le vase. L'eau se répand. Raphaël a les mains mouillées. Son ventre est serré. Il va vers maman, puis vers la cuisine. J'ai touché le vase. L'eau est par terre. Merci d'avoir raconté. On dit à papa ou maman ce qui s'est passé. Papa tend un torchon bleu. Le torchon est rêche. Raphaël aide à essuyer. Le parquet redevient mat. Raconter, c'est le geste. Bravo, Raphaël. Les fleurs se tiennent de nouveau. Plus tard, à la cuisine, un sac de farine attend. Le sac est en papier. Le papier fait un bruit sec. Un peu de farine tombe. Ça fait une trace blanche. Raphaël sent encore son ventre. Il va vers papa et maman. La farine est par terre. Merci de raconter. On essuie ensemble. Maman tend le torchon. Papa tient le sac. Raphaël passe le torchon tout doux. Au salon, puis à la cuisine. On raconte à papa ou maman. Tu as raconté les deux fois. Oui, maman. Raphaël se sent plus léger. Le pain sent encore bon.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Éric joue dans le salon. Un vase de fleurs penche. Il touche le vase. L'eau se répand. Éric a les mains mouillées. Son ventre est serré. Papa est dans la cuisine. Maman est près de la fenêtre. Éric va vers eux. Il va raconter.
-narrateur|J'ai touché le vase. L'eau est par terre. Papa écoute. Maman écoute.
-papa|Merci d'avoir raconté. On dit à papa ou maman ce qui s'est passé.
-narrateur|Éric aide à essuyer.
-maman|Raconter, c'est le geste. Même quand c'est une bêtise. Plus tard, à la cuisine, de la farine tombe. Même leçon, autre lieu.
-narrateur|Éric va raconter. Il dit à papa et maman : la farine est par terre. Papa sourit. Maman tend un torchon. Éric se sent plus léger.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le rideau se soulève un tout petit peu.
+narrateur|Un vent doux entre.
+narrateur|Une abeille tape la vitre, puis s'en va.
+narrateur|Des fleurs jaunes sont dans un vase.
+narrateur|L'eau du vase brille.
+narrateur|Une tige penche vers la lumière.
+narrateur|Papa est dans la cuisine.
+narrateur|Ça sent le pain chaud, là-bas.
+narrateur|Maman est près de la fenêtre.
+maman|Raphaël, tu as vu l'abeille ?
+enfant-m|Oui, maman.
+enfant-m|Elle est partie.
+maman|Elle a tapé tout doux.
+papa|Le pain est presque prêt.
+narrateur|En ce moment, Raphaël s'approche du vase.
+narrateur|Les fleurs sentent l'herbe coupée.
+narrateur|Il touche le vase.
+narrateur|L'eau se répand.
+narrateur|Raphaël a les mains mouillées.
+narrateur|Son ventre est serré.
+narrateur|Il va vers maman, puis vers la cuisine.
+enfant-m|J'ai touché le vase.
+enfant-m|L'eau est par terre.
+maman|Merci d'avoir raconté.
+papa|On dit à papa ou maman ce qui s'est passé.
+narrateur|Papa tend un torchon bleu.
+narrateur|Le torchon est rêche.
+narrateur|Raphaël aide à essuyer.
+narrateur|Le parquet redevient mat.
+maman|Raconter, c'est le geste.
+papa|Bravo, Raphaël.
+narrateur|Les fleurs se tiennent de nouveau.
+narrateur|Plus tard, à la cuisine, un sac de farine attend.
+narrateur|Le sac est en papier.
+narrateur|Le papier fait un bruit sec.
+narrateur|Un peu de farine tombe.
+narrateur|Ça fait une trace blanche.
+narrateur|Raphaël sent encore son ventre.
+narrateur|Il va vers papa et maman.
+enfant-m|La farine est par terre.
+papa|Merci de raconter.
+maman|On essuie ensemble.
+narrateur|Maman tend le torchon.
+narrateur|Papa tient le sac.
+narrateur|Raphaël passe le torchon tout doux.
+papa|Au salon, puis à la cuisine.
+papa|On raconte à papa ou maman.
+maman|Tu as raconté les deux fois.
+enfant-m|Oui, maman.
+narrateur|Raphaël se sent plus léger.
+narrateur|Le pain sent encore bon.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Éric a touché le vase. Que fait-il ?</t>
+          <t>Raphaël a touché le vase. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1501,10 +1557,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Éric a touché le vase. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël a touché le vase.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1529,7 +1585,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Éric a su raconter. Il a parlé à papa et maman. Au salon, puis à la cuisine.</t>
+          <t>Raphaël a su raconter. Il a parlé à papa et maman. Au salon, puis à la cuisine. Tu as dit ce qui s'est passé ? Oui, papa. Bravo. Tu as fait du bon travail. Le vase est de nouveau droit. Les fleurs jaunes tiennent bien. Le torchon sèche près de l'évier. Le parquet est sec ? Oui, papa. Une fleur penche encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,10 +1729,21 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Éric a su raconter. Il a parlé à papa et maman. Au salon, puis à la cuisine.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Raphaël a su raconter.
+narrateur|Il a parlé à papa et maman.
+narrateur|Au salon, puis à la cuisine.
+papa|Tu as dit ce qui s'est passé ?
+enfant-m|Oui, papa.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le vase est de nouveau droit.
+narrateur|Les fleurs jaunes tiennent bien.
+narrateur|Le torchon sèche près de l'évier.
+papa|Le parquet est sec ?
+enfant-m|Oui, papa.
+narrateur|Une fleur penche encore un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1701,7 +1768,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Éric pose le torchon. Maman lui tient la main.</t>
+          <t>Raphaël pose le torchon. Je te tiens la main ? Oui, maman. Maman lui tient la main. La main de maman est chaude. Tu as fini d'essuyer ? Oui, papa. Bravo. Le rideau bouge encore un peu. On goûte le pain ? Oui. Ça sent le chaud, tout près.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1841,10 +1908,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Éric pose le torchon. Maman lui tient la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Raphaël pose le torchon.
+maman|Je te tiens la main ?
+enfant-m|Oui, maman.
+narrateur|Maman lui tient la main.
+narrateur|La main de maman est chaude.
+papa|Tu as fini d'essuyer ?
+enfant-m|Oui, papa.
+papa|Bravo.
+narrateur|Le rideau bouge encore un peu.
+maman|On goûte le pain ?
+enfant-m|Oui.
+narrateur|Ça sent le chaud, tout près.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1869,7 +1946,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les fleurs sentent encore l'herbe. Merci d'avoir raconté. On dit à papa ou maman. Oui. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2009,10 +2086,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Les fleurs sentent encore l'herbe.
+maman|Merci d'avoir raconté.
+papa|On dit à papa ou maman.
+enfant-m|Oui.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2031,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2149,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-10.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-10.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Éric joue dans le salon. Un vase de fleurs penche. Il touche le vase. L'eau se répand. Éric a les mains mouillées. Son ventre est serré. Papa est dans la cuisine. Maman est près de la fenêtre. Éric va vers eux. Il va &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. Il dit : j'ai touché le vase. L'eau est par terre. Papa écoute. Maman écoute. Papa dit : merci d'avoir raconté. On dit à papa ou maman ce qui s'est passé. Éric aide à essuyer. Maman dit : raconter, c'est le geste. Même quand c'est une bêtise. Plus tard, à la cuisine, de la farine tombe. Même leçon, autre lieu. Éric va raconter. Il dit à papa et maman : la farine est par terre. Papa sourit. Maman tend un torchon. Éric se sent plus léger.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le rideau se soulève un tout petit peu. Un vent doux entre. Une abeille tape la vitre, puis s'en va. Des fleurs jaunes sont dans un vase. L'eau du vase brille. Une tige penche vers la lumière. Papa est dans la cuisine. Ça sent le pain chaud, là-bas. Maman est près de la fenêtre. Raphaël, tu as vu l'abeille ? Oui, maman. Elle est partie. Elle a tapé tout doux. Le pain est presque prêt. En ce moment, Raphaël s'approche du vase. Les fleurs sentent l'herbe coupée. Il touche le vase. L'eau se répand. Raphaël a les mains mouillées. Son ventre est serré. Il va vers maman, puis vers la cuisine. J'ai touché le vase. L'eau est par terre. Merci d'avoir raconté. On dit à papa ou maman ce qui s'est passé. Papa tend un torchon bleu. Le torchon est rêche. Raphaël aide à essuyer. Le parquet redevient mat. Raconter, c'est le geste. Bravo, Raphaël. Les fleurs se tiennent de nouveau. Plus tard, à la cuisine, un sac de farine attend. Le sac est en papier. Le papier fait un bruit sec. Un peu de farine tombe. Ça fait une trace blanche. Raphaël sent encore son ventre. Il va vers papa et maman. La farine est par terre. Merci de raconter. On essuie ensemble. Maman tend le torchon. Papa tient le sac. Raphaël passe le torchon tout doux. Au salon, puis à la cuisine. On raconte à papa ou maman. Tu as raconté les deux fois. Oui, maman. Raphaël se sent plus léger. Le pain sent encore bon.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Éric a touché le vase. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a touché le vase. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a su raconter. Il a parlé à papa et maman. Au salon, puis à la cuisine. Tu as dit ce qui s'est passé ? Oui, papa. Bravo. Tu as fait du bon travail. Le vase est de nouveau droit. Les fleurs jaunes tiennent bien. Le torchon sèche près de l'évier. Le parquet est sec ? Oui, papa. Une fleur penche encore un peu.</t>
+          <t>Raphaël a su raconter. Il a parlé à papa et maman. Au salon, puis à la cuisine. Tu as dit ce qui s'est passé ? Oui, papa. Bravo. Le vase est de nouveau droit. Les fleurs jaunes tiennent bien. Le torchon sèche près de l'évier. Le parquet est sec ? Oui, papa. Une fleur penche encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Éric a su &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. Il a parlé à papa et maman. Au salon, puis à la cuisine.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a su raconter. Il a parlé à papa et maman. Au salon, puis à la cuisine. Tu as dit ce qui s'est passé ? Oui, papa. Bravo. Le vase est de nouveau droit. Les fleurs jaunes tiennent bien. Le torchon sèche près de l'évier. Le parquet est sec ? Oui, papa. Une fleur penche encore un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1735,7 +1735,6 @@
 papa|Tu as dit ce qui s'est passé ?
 enfant-m|Oui, papa.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 narrateur|Le vase est de nouveau droit.
 narrateur|Les fleurs jaunes tiennent bien.
 narrateur|Le torchon sèche près de l'évier.
@@ -1773,7 +1772,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Éric pose le torchon. Maman lui tient la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël pose le torchon. Je te tiens la main ? Oui, maman. Maman lui tient la main. La main de maman est chaude. Tu as fini d'essuyer ? Oui, papa. Bravo. Le rideau bouge encore un peu. On goûte le pain ? Oui. Ça sent le chaud, tout près.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1946,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les fleurs sentent encore l'herbe. Merci d'avoir raconté. On dit à papa ou maman. Oui. L'histoire est finie.</t>
+          <t>Les fleurs sentent encore l'herbe. Merci d'avoir raconté. On dit à papa ou maman. Oui.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les fleurs sentent encore l'herbe. Merci d'avoir raconté. On dit à papa ou maman. Oui.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2089,8 +2088,7 @@
           <t>narrateur|Les fleurs sentent encore l'herbe.
 maman|Merci d'avoir raconté.
 papa|On dit à papa ou maman.
-enfant-m|Oui.
-narrateur|L'histoire est finie.</t>
+enfant-m|Oui.</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2156,6 +2154,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-10.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-10.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon puis cuisine</t>
+          <t>salon puis cuisine, rideau, fleurs, farine</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Éric, papa, maman</t>
+          <t>Raphaël, papa, maman</t>
         </is>
       </c>
     </row>
